--- a/sheets/민요/검수/창부타령-4.xlsx
+++ b/sheets/민요/검수/창부타령-4.xlsx
@@ -756,10 +756,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/창부타령-4.xlsx
+++ b/sheets/민요/검수/창부타령-4.xlsx
@@ -524,34 +524,9 @@
 소</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">姑
-無</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">仲姑</t>
-    </r>
+    <t xml:space="preserve">姑
+無南
+仲姑</t>
   </si>
   <si>
     <t xml:space="preserve">길
@@ -589,34 +564,9 @@
 적</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">–
-無</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無潢</t>
-    </r>
+    <t xml:space="preserve">–
+無南
+無潢</t>
   </si>
   <si>
     <t xml:space="preserve">노
@@ -628,34 +578,9 @@
 나</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">無</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">南
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="24"/>
-        <rFont val="궁서체"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">仲姑
+    <t xml:space="preserve">無南
+仲姑
 仲</t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">지
@@ -697,17 +622,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -829,7 +754,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="28">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -891,6 +816,54 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2351,234 +2324,234 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B1:I10"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="16" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="17" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="16" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="17" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="16" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="17" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="16" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="17" width="6"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="2" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="1" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="42.11" customHeight="true">
+      <c r="B2" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7" t="s">
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="93.77" customHeight="true">
+      <c r="B3" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="20" t="s">
         <v>121</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="20" t="s">
         <v>123</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="20" t="s">
         <v>125</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="21" t="s">
         <v>47</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="22" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="9" t="s">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="93.77" customHeight="true">
+      <c r="B4" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="D4" s="9" t="s">
+      <c r="D4" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="23" t="s">
         <v>130</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="F4" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="24" t="s">
         <v>132</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="24" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7" t="s">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="93.77" customHeight="true">
+      <c r="B5" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="C5" s="12" t="s">
+      <c r="C5" s="24" t="s">
         <v>135</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="G5" s="12" t="s">
+      <c r="G5" s="24" t="s">
         <v>138</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="24" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7" t="s">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="93.77" customHeight="true">
+      <c r="B6" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="C6" s="13" t="s">
+      <c r="C6" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="F6" s="21" t="s">
         <v>57</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="26" t="s">
         <v>76</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="I6" s="13" t="s">
+      <c r="I6" s="25" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="15" t="s">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="93.77" customHeight="true">
+      <c r="B7" s="27" t="s">
         <v>142</v>
       </c>
-      <c r="C7" s="8" t="s">
+      <c r="C7" s="20" t="s">
         <v>143</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="F7" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="G7" s="10" t="s">
+      <c r="G7" s="22" t="s">
         <v>146</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="20" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7" t="s">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="93.77" customHeight="true">
+      <c r="B8" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="C8" s="12" t="s">
+      <c r="C8" s="24" t="s">
         <v>149</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="E8" s="12"/>
-      <c r="F8" s="7" t="s">
+      <c r="E8" s="24"/>
+      <c r="F8" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="G8" s="12" t="s">
+      <c r="G8" s="24" t="s">
         <v>150</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="I8" s="12" t="s">
+      <c r="I8" s="24" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7" t="s">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="93.77" customHeight="true">
+      <c r="B9" s="19" t="s">
         <v>151</v>
       </c>
-      <c r="C9" s="12" t="s">
+      <c r="C9" s="24" t="s">
         <v>137</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="19" t="s">
         <v>103</v>
       </c>
-      <c r="E9" s="12"/>
-      <c r="F9" s="7" t="s">
+      <c r="E9" s="24"/>
+      <c r="F9" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="G9" s="12" t="s">
+      <c r="G9" s="24" t="s">
         <v>152</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="I9" s="12" t="s">
+      <c r="I9" s="24" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="77.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7" t="s">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="93.77" customHeight="true">
+      <c r="B10" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="E10" s="13"/>
-      <c r="F10" s="9" t="s">
+      <c r="E10" s="25"/>
+      <c r="F10" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="G10" s="14" t="s">
+      <c r="G10" s="26" t="s">
         <v>155</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="19" t="s">
         <v>67</v>
       </c>
-      <c r="I10" s="13" t="s">
+      <c r="I10" s="25" t="s">
         <v>156</v>
       </c>
     </row>
@@ -2588,7 +2561,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="95"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/창부타령-4.xlsx
+++ b/sheets/민요/검수/창부타령-4.xlsx
@@ -2330,13 +2330,13 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="16" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="16" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="17" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="16" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="16" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="17" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="16" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="16" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="17" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="16" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="16" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="17" width="6"/>
   </cols>
   <sheetData>
